--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.823659236986653</v>
+        <v>1.108844626010331</v>
       </c>
       <c r="D2" t="n">
-        <v>6.894671542615499</v>
+        <v>1.120384125675019</v>
       </c>
       <c r="E2" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F2" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.7402128428141</v>
+        <v>5.320284586957292</v>
       </c>
       <c r="D3" t="n">
-        <v>32.85206075636921</v>
+        <v>5.338459872909996</v>
       </c>
       <c r="E3" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F3" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.91744562643265</v>
+        <v>5.999084914295305</v>
       </c>
       <c r="D4" t="n">
-        <v>36.67028374026214</v>
+        <v>5.958921107792597</v>
       </c>
       <c r="E4" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F4" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.36692226284029</v>
+        <v>5.584624867711548</v>
       </c>
       <c r="D5" t="n">
-        <v>34.14697237136114</v>
+        <v>5.548883010346185</v>
       </c>
       <c r="E5" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F5" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.50842694744988</v>
+        <v>5.445119378960605</v>
       </c>
       <c r="D6" t="n">
-        <v>33.45629784296797</v>
+        <v>5.436648399482295</v>
       </c>
       <c r="E6" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F6" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.88926515513212</v>
+        <v>2.907005587708969</v>
       </c>
       <c r="D7" t="n">
-        <v>18.64185248170219</v>
+        <v>3.029301028276606</v>
       </c>
       <c r="E7" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F7" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.98026383788408</v>
+        <v>2.921792873656163</v>
       </c>
       <c r="D8" t="n">
-        <v>18.21451563219153</v>
+        <v>2.959858790231124</v>
       </c>
       <c r="E8" t="n">
-        <v>10.61256466546017</v>
+        <v>1.724541758137278</v>
       </c>
       <c r="F8" t="n">
-        <v>10.43595866672378</v>
+        <v>1.695843283342614</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
